--- a/erp-server/erp-server-mrp/src/main/resources/excel/replenishmentRule.xlsx
+++ b/erp-server/erp-server-mrp/src/main/resources/excel/replenishmentRule.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="95">
   <si>
     <r>
       <rPr>
@@ -126,6 +126,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFF54A45"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -140,6 +147,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -155,6 +169,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -170,6 +191,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -185,6 +213,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -200,6 +235,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -215,6 +257,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -368,6 +417,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -425,6 +481,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -449,6 +512,87 @@
   </si>
   <si>
     <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>默认日销量类型</t>
+    </r>
+  </si>
+  <si>
+    <t>固定日销量</t>
+  </si>
+  <si>
+    <t>动态日销量</t>
+  </si>
+  <si>
+    <t>3天日均（%）</t>
+  </si>
+  <si>
+    <t>7天日均（%）</t>
+  </si>
+  <si>
+    <t>14天日均（%）</t>
+  </si>
+  <si>
+    <t>30天日均（%）</t>
+  </si>
+  <si>
+    <t>60天日均（%）</t>
+  </si>
+  <si>
+    <t>90天日均（%）</t>
+  </si>
+  <si>
+    <t>180天日均（%）</t>
+  </si>
+  <si>
+    <t>270天日均（%）</t>
+  </si>
+  <si>
+    <t>360天日均（%）</t>
+  </si>
+  <si>
+    <t>{.defaultTypeName}</t>
+  </si>
+  <si>
+    <t>{.fixedValue}</t>
+  </si>
+  <si>
+    <t>{.threeDaysRatio}</t>
+  </si>
+  <si>
+    <t>{.sevenDaysRatio}</t>
+  </si>
+  <si>
+    <t>{.fourteenDaysRatio}</t>
+  </si>
+  <si>
+    <t>{.thirtyDaysRatio}</t>
+  </si>
+  <si>
+    <t>{.sixtyDaysRatio}</t>
+  </si>
+  <si>
+    <t>{.ninetyDaysRatio}</t>
+  </si>
+  <si>
+    <t>{.oneHundredEightyDaysRatio}</t>
+  </si>
+  <si>
+    <t>{.twoHundredSeventyDaysRatio}</t>
+  </si>
+  <si>
+    <t>{.threeHundredSixtyDaysRatio}</t>
+  </si>
+  <si>
+    <r>
       <rPr>
         <sz val="10"/>
         <color rgb="FFFF0000"/>
@@ -466,124 +610,8 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>默认日销量类型</t>
-    </r>
-  </si>
-  <si>
-    <t>固定日销量</t>
-  </si>
-  <si>
-    <t>动态日销量</t>
-  </si>
-  <si>
-    <t>3天日均（%）</t>
-  </si>
-  <si>
-    <t>7天日均（%）</t>
-  </si>
-  <si>
-    <t>14天日均（%）</t>
-  </si>
-  <si>
-    <t>30天日均（%）</t>
-  </si>
-  <si>
-    <t>60天日均（%）</t>
-  </si>
-  <si>
-    <t>90天日均（%）</t>
-  </si>
-  <si>
-    <t>180天日均（%）</t>
-  </si>
-  <si>
-    <t>270天日均（%）</t>
-  </si>
-  <si>
-    <t>360天日均（%）</t>
-  </si>
-  <si>
-    <t>{.defaultTypeName}</t>
-  </si>
-  <si>
-    <t>{.fixedValue}</t>
-  </si>
-  <si>
-    <t>{.threeDaysRatio}</t>
-  </si>
-  <si>
-    <t>{.sevenDaysRatio}</t>
-  </si>
-  <si>
-    <t>{.fourteenDaysRatio}</t>
-  </si>
-  <si>
-    <t>{.thirtyDaysRatio}</t>
-  </si>
-  <si>
-    <t>{.sixtyDaysRatio}</t>
-  </si>
-  <si>
-    <t>{.ninetyDaysRatio}</t>
-  </si>
-  <si>
-    <t>{.oneHundredEightyDaysRatio}</t>
-  </si>
-  <si>
-    <t>{.twoHundredSeventyDaysRatio}</t>
-  </si>
-  <si>
-    <t>{.threeHundredSixtyDaysRatio}</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>规则名称</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>动态日销量</t>
     </r>
-  </si>
-  <si>
-    <t>{.startDateStr}</t>
-  </si>
-  <si>
-    <t>{.endDateStr}</t>
   </si>
   <si>
     <r>
@@ -1959,7 +1987,7 @@
     <col min="7" max="7" width="15.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" ht="14.25" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2067,7 +2095,7 @@
       <c r="R1" s="4"/>
       <c r="S1" s="4"/>
     </row>
-    <row r="2" ht="14.25" spans="1:19">
+    <row r="2" spans="1:19">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -2198,7 +2226,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>88</v>
+        <v>58</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>59</v>
@@ -2207,7 +2235,7 @@
         <v>60</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
@@ -2277,10 +2305,10 @@
         <v>62</v>
       </c>
       <c r="E3" t="s">
-        <v>90</v>
+        <v>63</v>
       </c>
       <c r="F3" t="s">
-        <v>91</v>
+        <v>64</v>
       </c>
       <c r="G3" t="s">
         <v>79</v>
@@ -2351,7 +2379,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>88</v>
+        <v>58</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>59</v>
@@ -2360,7 +2388,7 @@
         <v>60</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="H1" s="4"/>
       <c r="I1" s="4"/>
@@ -2432,7 +2460,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>88</v>
+        <v>58</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>59</v>
@@ -2441,13 +2469,13 @@
         <v>60</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="J1" s="4"/>
       <c r="K1" s="4"/>
@@ -2483,10 +2511,10 @@
         <v>64</v>
       </c>
       <c r="G2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="H2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="I2" t="s">
         <v>78</v>

--- a/erp-server/erp-server-mrp/src/main/resources/excel/replenishmentRule.xlsx
+++ b/erp-server/erp-server-mrp/src/main/resources/excel/replenishmentRule.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" activeTab="1"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="备货" sheetId="1" r:id="rId1"/>
@@ -125,157 +125,25 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFF54A45"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>安全天数</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>默认备货系数</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>采购审批（天）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>生产周期（天）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>供应商发货（天）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>质检入库（天）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>采购频率（天）</t>
-    </r>
+    <t>安全天数</t>
+  </si>
+  <si>
+    <t>默认备货系数</t>
+  </si>
+  <si>
+    <t>采购审批（天）</t>
+  </si>
+  <si>
+    <t>生产周期（天）</t>
+  </si>
+  <si>
+    <t>供应商发货（天）</t>
+  </si>
+  <si>
+    <t>质检入库（天）</t>
+  </si>
+  <si>
+    <t>采购频率（天）</t>
   </si>
   <si>
     <t>物流时效（空运）</t>
@@ -722,6 +590,12 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -868,12 +742,6 @@
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1254,137 +1122,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1425,6 +1293,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1799,10 +1670,10 @@
       <c r="X1" s="13"/>
       <c r="Y1" s="13"/>
       <c r="Z1" s="13"/>
-      <c r="AA1" s="13" t="s">
+      <c r="AA1" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="AB1" s="12" t="s">
+      <c r="AB1" s="10" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1810,19 +1681,19 @@
       <c r="A2" s="11"/>
       <c r="B2" s="11"/>
       <c r="C2" s="11"/>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="H2" s="11" t="s">
         <v>11</v>
       </c>
       <c r="I2" s="11" t="s">
